--- a/astro-site/public/dl/pastry-shop-checklist-templates/04-pastry-chef-duties-by-role.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/04-pastry-chef-duties-by-role.xlsx
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Prepare custom orders (custom cakes) → 11 Cake Orders · sheet "Order Form"</t>
+          <t>Prepare custom orders (custom cakes); with a CONFIRMED allergy, make that order first thing in the day on a cleaned and sanitized bench with clean tools, and label it on its own → 11 Cake Orders · sheet "Order Form"</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Prepare boxes and to-go packaging</t>
+          <t>Prepare boxes and to-go packaging; pick up pastries with tongs or bakery tissue, never bare hands (FDA Food Code 3-301.11)</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
